--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="505">
   <si>
     <t>Filename</t>
   </si>
@@ -817,16 +817,25 @@
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,0,0,1</t>
   </si>
   <si>
     <t>0.9890,0.0008,0.0033,0.0000</t>
   </si>
   <si>
-    <t>0.9382,0.0094,0.0022,0.0030</t>
+    <t>0.9380,0.0094,0.0022,0.0030</t>
   </si>
   <si>
     <t>0.9942,0.0019,0.0007,0.0000</t>
@@ -862,100 +871,100 @@
     <t>0.9383,0.0044,0.0286,0.0001</t>
   </si>
   <si>
-    <t>0.4526,0.0103,0.5140,0.0004</t>
-  </si>
-  <si>
-    <t>0.8056,0.0003,0.2671,0.0000</t>
-  </si>
-  <si>
-    <t>0.2463,0.0042,0.7969,0.0003</t>
+    <t>0.4529,0.0103,0.5135,0.0004</t>
+  </si>
+  <si>
+    <t>0.8056,0.0003,0.2670,0.0000</t>
+  </si>
+  <si>
+    <t>0.2466,0.0042,0.7965,0.0003</t>
   </si>
   <si>
     <t>0.9708,0.0007,0.0167,0.0000</t>
   </si>
   <si>
-    <t>0.0686,0.9652,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.2731,0.8123,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.1675,0.9595,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4506,0.6719,0.0005,0.0000</t>
+    <t>0.0684,0.9653,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.2723,0.8130,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.1670,0.9596,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4498,0.6727,0.0005,0.0000</t>
   </si>
   <si>
     <t>0.0105,0.9958,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.7214,0.0026,0.2938,0.0002</t>
-  </si>
-  <si>
-    <t>0.2517,0.0104,0.7632,0.0008</t>
-  </si>
-  <si>
-    <t>0.1820,0.0004,0.9126,0.0000</t>
-  </si>
-  <si>
-    <t>0.1414,0.0032,0.9051,0.0003</t>
-  </si>
-  <si>
-    <t>0.3860,0.0025,0.6977,0.0002</t>
-  </si>
-  <si>
-    <t>0.1845,0.0010,0.8991,0.0001</t>
+    <t>0.7215,0.0026,0.2935,0.0002</t>
+  </si>
+  <si>
+    <t>0.2520,0.0104,0.7628,0.0008</t>
+  </si>
+  <si>
+    <t>0.1822,0.0004,0.9125,0.0000</t>
+  </si>
+  <si>
+    <t>0.1416,0.0033,0.9049,0.0003</t>
+  </si>
+  <si>
+    <t>0.3860,0.0025,0.6976,0.0002</t>
+  </si>
+  <si>
+    <t>0.1847,0.0010,0.8990,0.0001</t>
   </si>
   <si>
     <t>0.0231,0.0002,0.9909,0.0000</t>
   </si>
   <si>
-    <t>0.9725,0.0129,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.9627,0.0447,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.2759,0.0010,0.8045,0.0001</t>
-  </si>
-  <si>
-    <t>0.6584,0.0799,0.0684,0.0003</t>
+    <t>0.9724,0.0129,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.9626,0.0448,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.2760,0.0010,0.8042,0.0001</t>
+  </si>
+  <si>
+    <t>0.6580,0.0802,0.0682,0.0003</t>
   </si>
   <si>
     <t>0.9920,0.0045,0.0012,0.0000</t>
   </si>
   <si>
-    <t>0.9848,0.0044,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.9788,0.0263,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.6364,0.4089,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9259,0.4446,0.0018</t>
-  </si>
-  <si>
-    <t>0.0058,0.0065,0.9883,0.0017</t>
-  </si>
-  <si>
-    <t>0.0123,0.1163,0.9124,0.0010</t>
-  </si>
-  <si>
-    <t>0.1246,0.0196,0.7197,0.0109</t>
-  </si>
-  <si>
-    <t>0.0016,0.9000,0.3353,0.0021</t>
-  </si>
-  <si>
-    <t>0.0044,0.9841,0.0241,0.0013</t>
+    <t>0.9848,0.0045,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.9788,0.0264,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.6353,0.4102,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9261,0.4440,0.0018</t>
+  </si>
+  <si>
+    <t>0.0058,0.0066,0.9883,0.0017</t>
+  </si>
+  <si>
+    <t>0.0123,0.1167,0.9122,0.0010</t>
+  </si>
+  <si>
+    <t>0.1245,0.0197,0.7191,0.0109</t>
+  </si>
+  <si>
+    <t>0.0016,0.9004,0.3343,0.0021</t>
+  </si>
+  <si>
+    <t>0.0044,0.9842,0.0241,0.0013</t>
   </si>
   <si>
     <t>0.0083,0.0095,0.9886,0.0003</t>
   </si>
   <si>
-    <t>0.4446,0.3503,0.0072,0.0089</t>
+    <t>0.4440,0.3512,0.0072,0.0088</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0000,0.0000</t>
@@ -970,19 +979,19 @@
     <t>0.0013,0.0213,0.9916,0.0007</t>
   </si>
   <si>
-    <t>0.0021,0.2426,0.8883,0.0030</t>
-  </si>
-  <si>
-    <t>0.0268,0.0025,0.9812,0.0003</t>
-  </si>
-  <si>
-    <t>0.2959,0.0004,0.8365,0.0000</t>
+    <t>0.0021,0.2436,0.8879,0.0030</t>
+  </si>
+  <si>
+    <t>0.0269,0.0025,0.9812,0.0003</t>
+  </si>
+  <si>
+    <t>0.2959,0.0004,0.8364,0.0000</t>
   </si>
   <si>
     <t>0.0214,0.0016,0.9866,0.0001</t>
   </si>
   <si>
-    <t>0.0554,0.0067,0.9536,0.0005</t>
+    <t>0.0555,0.0067,0.9534,0.0005</t>
   </si>
   <si>
     <t>0.9984,0.0009,0.0001,0.0000</t>
@@ -1006,22 +1015,22 @@
     <t>0.9991,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9972,0.8120,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0240,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.0085,0.9948,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.9687,0.7931,0.0007</t>
+    <t>0.0000,0.9972,0.8117,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0240,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.0086,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9688,0.7927,0.0007</t>
   </si>
   <si>
     <t>0.0021,0.0036,0.9964,0.0007</t>
   </si>
   <si>
-    <t>0.0216,0.9845,0.0017,0.0000</t>
+    <t>0.0215,0.9846,0.0016,0.0000</t>
   </si>
   <si>
     <t>0.0004,0.9997,0.0003,0.0000</t>
@@ -1033,55 +1042,55 @@
     <t>0.9334,0.0074,0.0224,0.0001</t>
   </si>
   <si>
-    <t>0.6226,0.0009,0.4442,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.4597,0.9797,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.8994,0.9302,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.2432,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9720,0.8291,0.0003</t>
-  </si>
-  <si>
-    <t>0.6881,0.0139,0.0070,0.0581</t>
-  </si>
-  <si>
-    <t>0.7153,0.0202,0.0009,0.0379</t>
-  </si>
-  <si>
-    <t>0.8467,0.0070,0.0007,0.0218</t>
-  </si>
-  <si>
-    <t>0.8847,0.0122,0.0011,0.0128</t>
-  </si>
-  <si>
-    <t>0.9255,0.0130,0.0046,0.0033</t>
-  </si>
-  <si>
-    <t>0.4905,0.0133,0.0038,0.1844</t>
-  </si>
-  <si>
-    <t>0.0002,0.9967,0.2342,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.6795,0.9882,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.8762,0.5538,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.4744,0.9694,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9892,0.9574,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9925,0.0847,0.0006</t>
+    <t>0.6226,0.0009,0.4440,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.4608,0.9796,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.8997,0.9300,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.2428,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9721,0.8287,0.0003</t>
+  </si>
+  <si>
+    <t>0.6878,0.0139,0.0070,0.0581</t>
+  </si>
+  <si>
+    <t>0.7148,0.0203,0.0009,0.0379</t>
+  </si>
+  <si>
+    <t>0.8463,0.0071,0.0007,0.0219</t>
+  </si>
+  <si>
+    <t>0.8844,0.0122,0.0011,0.0128</t>
+  </si>
+  <si>
+    <t>0.9254,0.0131,0.0046,0.0033</t>
+  </si>
+  <si>
+    <t>0.4896,0.0133,0.0038,0.1847</t>
+  </si>
+  <si>
+    <t>0.0002,0.9967,0.2337,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.6802,0.9882,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.8767,0.5529,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.4752,0.9693,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9892,0.9573,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9925,0.0845,0.0006</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
@@ -1096,7 +1105,7 @@
     <t>0.9990,0.0004,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9976,0.0050,0.0002,0.0000</t>
+    <t>0.9975,0.0050,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0001,0.0000</t>
@@ -1117,49 +1126,49 @@
     <t>0.0070,0.0002,0.9974,0.0000</t>
   </si>
   <si>
-    <t>0.2318,0.0025,0.8257,0.0002</t>
-  </si>
-  <si>
-    <t>0.9203,0.0002,0.0994,0.0000</t>
-  </si>
-  <si>
-    <t>0.2205,0.0013,0.8516,0.0001</t>
-  </si>
-  <si>
-    <t>0.0130,0.9933,0.0001,0.0000</t>
+    <t>0.2318,0.0025,0.8256,0.0002</t>
+  </si>
+  <si>
+    <t>0.9203,0.0002,0.0993,0.0000</t>
+  </si>
+  <si>
+    <t>0.2208,0.0013,0.8513,0.0001</t>
+  </si>
+  <si>
+    <t>0.0129,0.9933,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0125,0.9944,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.6081,0.7413,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8139,0.3069,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0164,0.9915,0.0001,0.0000</t>
+    <t>0.6073,0.7421,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8133,0.3078,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0163,0.9915,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0014,0.9993,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9870,0.0116,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.7966,0.0169,0.1062,0.0003</t>
-  </si>
-  <si>
-    <t>0.2581,0.0044,0.7851,0.0004</t>
-  </si>
-  <si>
-    <t>0.7783,0.0121,0.1383,0.0003</t>
-  </si>
-  <si>
-    <t>0.7363,0.0121,0.1916,0.0003</t>
-  </si>
-  <si>
-    <t>0.0341,0.8517,0.0592,0.0624</t>
+    <t>0.9869,0.0116,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.7964,0.0170,0.1061,0.0003</t>
+  </si>
+  <si>
+    <t>0.2582,0.0044,0.7848,0.0004</t>
+  </si>
+  <si>
+    <t>0.7785,0.0121,0.1380,0.0003</t>
+  </si>
+  <si>
+    <t>0.7363,0.0122,0.1913,0.0003</t>
+  </si>
+  <si>
+    <t>0.0341,0.8521,0.0591,0.0622</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
@@ -1171,13 +1180,13 @@
     <t>0.0004,0.9992,0.0030,0.0004</t>
   </si>
   <si>
-    <t>0.1017,0.9493,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9885,0.0099,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9819,0.0183,0.0006,0.0000</t>
+    <t>0.1014,0.9494,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0100,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9819,0.0184,0.0006,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0000</t>
@@ -1192,13 +1201,13 @@
     <t>0.9992,0.0003,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0011,0.9027,0.7437,0.0009</t>
-  </si>
-  <si>
-    <t>0.0019,0.0962,0.9900,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0457,0.9940,0.0004</t>
+    <t>0.0011,0.9031,0.7429,0.0009</t>
+  </si>
+  <si>
+    <t>0.0019,0.0965,0.9900,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0458,0.9940,0.0004</t>
   </si>
   <si>
     <t>0.0098,0.0097,0.9874,0.0001</t>
@@ -1207,49 +1216,49 @@
     <t>0.9715,0.0012,0.0163,0.0000</t>
   </si>
   <si>
-    <t>0.8685,0.0387,0.0212,0.0001</t>
-  </si>
-  <si>
-    <t>0.5235,0.0002,0.6572,0.0000</t>
-  </si>
-  <si>
-    <t>0.9201,0.0042,0.0400,0.0001</t>
-  </si>
-  <si>
-    <t>0.9554,0.0081,0.0010,0.0024</t>
-  </si>
-  <si>
-    <t>0.0144,0.0303,0.0020,0.9842</t>
-  </si>
-  <si>
-    <t>0.0953,0.0168,0.0015,0.8500</t>
-  </si>
-  <si>
-    <t>0.8913,0.0049,0.0023,0.0099</t>
-  </si>
-  <si>
-    <t>0.0002,0.9832,0.7408,0.0003</t>
+    <t>0.8682,0.0388,0.0212,0.0001</t>
+  </si>
+  <si>
+    <t>0.5236,0.0002,0.6570,0.0000</t>
+  </si>
+  <si>
+    <t>0.9200,0.0042,0.0400,0.0001</t>
+  </si>
+  <si>
+    <t>0.9553,0.0081,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.0144,0.0305,0.0020,0.9842</t>
+  </si>
+  <si>
+    <t>0.0951,0.0169,0.0015,0.8501</t>
+  </si>
+  <si>
+    <t>0.8911,0.0049,0.0023,0.0099</t>
+  </si>
+  <si>
+    <t>0.0002,0.9833,0.7403,0.0003</t>
   </si>
   <si>
     <t>0.9983,0.0005,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9525,0.0489,0.0012,0.0000</t>
+    <t>0.9523,0.0491,0.0012,0.0000</t>
   </si>
   <si>
     <t>0.9986,0.0002,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.9851,0.0158,0.0007,0.0000</t>
+    <t>0.9851,0.0159,0.0007,0.0000</t>
   </si>
   <si>
     <t>0.9986,0.0001,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.5226,0.0000,0.6732,0.0000</t>
-  </si>
-  <si>
-    <t>0.9516,0.0000,0.0602,0.0000</t>
+    <t>0.5222,0.0000,0.6735,0.0000</t>
+  </si>
+  <si>
+    <t>0.9515,0.0000,0.0603,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9999,0.0000</t>
@@ -1261,7 +1270,7 @@
     <t>0.9958,0.0016,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.9553,0.0400,0.0021,0.0000</t>
+    <t>0.9552,0.0401,0.0021,0.0000</t>
   </si>
   <si>
     <t>0.9976,0.0003,0.0005,0.0000</t>
@@ -1270,7 +1279,7 @@
     <t>0.9921,0.0021,0.0012,0.0000</t>
   </si>
   <si>
-    <t>0.9007,0.0513,0.0100,0.0002</t>
+    <t>0.9005,0.0515,0.0099,0.0002</t>
   </si>
   <si>
     <t>0.9917,0.0009,0.0021,0.0000</t>
@@ -1288,10 +1297,10 @@
     <t>0.9992,0.0001,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9739,0.0505,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9843,0.0109,0.0012,0.0000</t>
+    <t>0.9738,0.0507,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9843,0.0110,0.0012,0.0000</t>
   </si>
   <si>
     <t>0.9940,0.0062,0.0003,0.0000</t>
@@ -1312,7 +1321,7 @@
     <t>0.9984,0.0005,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.8552,0.0004,0.1653,0.0000</t>
+    <t>0.8554,0.0004,0.1651,0.0000</t>
   </si>
   <si>
     <t>0.9980,0.0005,0.0003,0.0000</t>
@@ -1321,55 +1330,55 @@
     <t>0.0024,0.0009,0.9982,0.0000</t>
   </si>
   <si>
-    <t>0.0025,0.1252,0.9386,0.0020</t>
-  </si>
-  <si>
-    <t>0.4244,0.0087,0.5284,0.0003</t>
-  </si>
-  <si>
-    <t>0.0176,0.0536,0.9325,0.0012</t>
-  </si>
-  <si>
-    <t>0.0241,0.0116,0.9670,0.0005</t>
+    <t>0.0025,0.1257,0.9384,0.0020</t>
+  </si>
+  <si>
+    <t>0.4243,0.0088,0.5277,0.0003</t>
+  </si>
+  <si>
+    <t>0.0176,0.0538,0.9323,0.0012</t>
+  </si>
+  <si>
+    <t>0.0241,0.0117,0.9669,0.0005</t>
   </si>
   <si>
     <t>0.0134,0.0003,0.9945,0.0000</t>
   </si>
   <si>
-    <t>0.1142,0.0019,0.9279,0.0001</t>
-  </si>
-  <si>
-    <t>0.4639,0.0055,0.5568,0.0003</t>
-  </si>
-  <si>
-    <t>0.6763,0.0005,0.4182,0.0000</t>
-  </si>
-  <si>
-    <t>0.8337,0.0134,0.0925,0.0003</t>
-  </si>
-  <si>
-    <t>0.5407,0.0220,0.3141,0.0004</t>
-  </si>
-  <si>
-    <t>0.4635,0.0195,0.3961,0.0003</t>
-  </si>
-  <si>
-    <t>0.6111,0.0011,0.4568,0.0001</t>
-  </si>
-  <si>
-    <t>0.7740,0.0073,0.1608,0.0002</t>
-  </si>
-  <si>
-    <t>0.7513,0.0216,0.1273,0.0003</t>
-  </si>
-  <si>
-    <t>0.8262,0.4412,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9275,0.1248,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9899,0.0112,0.0004,0.0000</t>
+    <t>0.1143,0.0019,0.9278,0.0001</t>
+  </si>
+  <si>
+    <t>0.4642,0.0055,0.5563,0.0003</t>
+  </si>
+  <si>
+    <t>0.6765,0.0005,0.4178,0.0000</t>
+  </si>
+  <si>
+    <t>0.8336,0.0134,0.0924,0.0003</t>
+  </si>
+  <si>
+    <t>0.5407,0.0221,0.3137,0.0004</t>
+  </si>
+  <si>
+    <t>0.4635,0.0195,0.3955,0.0003</t>
+  </si>
+  <si>
+    <t>0.6112,0.0011,0.4564,0.0001</t>
+  </si>
+  <si>
+    <t>0.7742,0.0073,0.1605,0.0002</t>
+  </si>
+  <si>
+    <t>0.7512,0.0217,0.1272,0.0003</t>
+  </si>
+  <si>
+    <t>0.8257,0.4422,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9272,0.1253,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9898,0.0112,0.0004,0.0000</t>
   </si>
   <si>
     <t>0.9984,0.0011,0.0001,0.0000</t>
@@ -1378,34 +1387,34 @@
     <t>0.9959,0.0048,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.7484,0.1037,0.0215,0.0001</t>
+    <t>0.7479,0.1041,0.0214,0.0001</t>
   </si>
   <si>
     <t>0.9738,0.0027,0.0086,0.0000</t>
   </si>
   <si>
-    <t>0.6791,0.0310,0.1900,0.0011</t>
-  </si>
-  <si>
-    <t>0.5600,0.0013,0.5090,0.0003</t>
-  </si>
-  <si>
-    <t>0.9115,0.0048,0.0451,0.0001</t>
-  </si>
-  <si>
-    <t>0.1580,0.0025,0.8875,0.0004</t>
-  </si>
-  <si>
-    <t>0.0336,0.0755,0.7363,0.0039</t>
-  </si>
-  <si>
-    <t>0.0262,0.2977,0.6131,0.0019</t>
-  </si>
-  <si>
-    <t>0.0069,0.0232,0.9860,0.0005</t>
-  </si>
-  <si>
-    <t>0.0095,0.1783,0.8297,0.0007</t>
+    <t>0.6791,0.0311,0.1895,0.0011</t>
+  </si>
+  <si>
+    <t>0.5602,0.0013,0.5086,0.0003</t>
+  </si>
+  <si>
+    <t>0.9115,0.0048,0.0450,0.0001</t>
+  </si>
+  <si>
+    <t>0.1581,0.0025,0.8873,0.0004</t>
+  </si>
+  <si>
+    <t>0.0336,0.0761,0.7351,0.0039</t>
+  </si>
+  <si>
+    <t>0.0262,0.2992,0.6119,0.0019</t>
+  </si>
+  <si>
+    <t>0.0069,0.0233,0.9860,0.0005</t>
+  </si>
+  <si>
+    <t>0.0095,0.1792,0.8291,0.0007</t>
   </si>
   <si>
     <t>0.9994,0.0003,0.0001,0.0000</t>
@@ -1426,10 +1435,10 @@
     <t>0.9991,0.0004,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.8221,0.0021,0.1640,0.0000</t>
-  </si>
-  <si>
-    <t>0.9084,0.0105,0.0320,0.0000</t>
+    <t>0.8222,0.0021,0.1639,0.0000</t>
+  </si>
+  <si>
+    <t>0.9083,0.0106,0.0320,0.0000</t>
   </si>
   <si>
     <t>0.9655,0.0015,0.0177,0.0000</t>
@@ -1438,16 +1447,16 @@
     <t>0.0066,0.0011,0.9955,0.0001</t>
   </si>
   <si>
-    <t>0.0026,0.0028,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.0300,0.0073,0.9696,0.0004</t>
+    <t>0.0027,0.0028,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0300,0.0073,0.9695,0.0004</t>
   </si>
   <si>
     <t>0.0004,0.0001,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0322,0.0036,0.9752,0.0002</t>
+    <t>0.0323,0.0036,0.9752,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
@@ -1456,16 +1465,16 @@
     <t>0.0094,0.0021,0.9923,0.0001</t>
   </si>
   <si>
-    <t>0.4327,0.0281,0.4149,0.0007</t>
-  </si>
-  <si>
-    <t>0.8644,0.0011,0.1340,0.0001</t>
-  </si>
-  <si>
-    <t>0.8858,0.0011,0.0992,0.0002</t>
-  </si>
-  <si>
-    <t>0.9592,0.0039,0.0163,0.0000</t>
+    <t>0.4327,0.0282,0.4144,0.0007</t>
+  </si>
+  <si>
+    <t>0.8643,0.0011,0.1341,0.0001</t>
+  </si>
+  <si>
+    <t>0.8858,0.0011,0.0991,0.0002</t>
+  </si>
+  <si>
+    <t>0.9591,0.0039,0.0163,0.0000</t>
   </si>
   <si>
     <t>0.9993,0.0006,0.0000,0.0000</t>
@@ -1480,25 +1489,25 @@
     <t>0.9986,0.0006,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0231,0.0094,0.9713,0.0002</t>
-  </si>
-  <si>
-    <t>0.0042,0.0041,0.9952,0.0000</t>
+    <t>0.0231,0.0095,0.9712,0.0002</t>
+  </si>
+  <si>
+    <t>0.0042,0.0042,0.9952,0.0000</t>
   </si>
   <si>
     <t>0.0040,0.0020,0.9963,0.0000</t>
   </si>
   <si>
-    <t>0.1110,0.0157,0.8733,0.0006</t>
+    <t>0.1112,0.0157,0.8730,0.0006</t>
   </si>
   <si>
     <t>0.0234,0.0014,0.9858,0.0001</t>
   </si>
   <si>
-    <t>0.5907,0.2749,0.0121,0.0072</t>
-  </si>
-  <si>
-    <t>0.3621,0.0679,0.2917,0.0042</t>
+    <t>0.5898,0.2759,0.0121,0.0072</t>
+  </si>
+  <si>
+    <t>0.3619,0.0683,0.2909,0.0042</t>
   </si>
   <si>
     <t>0.0060,0.0023,0.9937,0.0005</t>
@@ -1507,19 +1516,19 @@
     <t>0.9967,0.0002,0.0009,0.0000</t>
   </si>
   <si>
-    <t>0.6746,0.0233,0.0052,0.0402</t>
-  </si>
-  <si>
-    <t>0.9439,0.0009,0.0024,0.0069</t>
+    <t>0.6741,0.0234,0.0052,0.0402</t>
+  </si>
+  <si>
+    <t>0.9438,0.0009,0.0024,0.0070</t>
   </si>
   <si>
     <t>0.1098,0.0011,0.0046,0.9177</t>
   </si>
   <si>
-    <t>0.6379,0.0005,0.0052,0.1208</t>
-  </si>
-  <si>
-    <t>0.9573,0.0036,0.0165,0.0004</t>
+    <t>0.6374,0.0005,0.0052,0.1211</t>
+  </si>
+  <si>
+    <t>0.9572,0.0036,0.0165,0.0004</t>
   </si>
 </sst>
 </file>
@@ -1905,7 +1914,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1919,7 +1928,7 @@
         <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1933,7 +1942,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1947,7 +1956,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1961,7 +1970,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1975,7 +1984,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1989,7 +1998,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2003,7 +2012,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2017,7 +2026,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2031,7 +2040,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2045,7 +2054,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2059,7 +2068,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2073,7 +2082,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2087,7 +2096,7 @@
         <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2101,7 +2110,7 @@
         <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2115,7 +2124,7 @@
         <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2129,7 +2138,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2143,7 +2152,7 @@
         <v>266</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2157,7 +2166,7 @@
         <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2171,7 +2180,7 @@
         <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2185,7 +2194,7 @@
         <v>266</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2199,7 +2208,7 @@
         <v>266</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2213,7 +2222,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2227,7 +2236,7 @@
         <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2241,7 +2250,7 @@
         <v>265</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2255,7 +2264,7 @@
         <v>265</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2269,7 +2278,7 @@
         <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2283,7 +2292,7 @@
         <v>265</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2297,7 +2306,7 @@
         <v>265</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2311,7 +2320,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2325,7 +2334,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2339,7 +2348,7 @@
         <v>265</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2353,7 +2362,7 @@
         <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2367,7 +2376,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2381,7 +2390,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2395,7 +2404,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2409,7 +2418,7 @@
         <v>264</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2423,7 +2432,7 @@
         <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2437,7 +2446,7 @@
         <v>265</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2451,7 +2460,7 @@
         <v>265</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2465,7 +2474,7 @@
         <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2479,7 +2488,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2493,7 +2502,7 @@
         <v>266</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2507,7 +2516,7 @@
         <v>265</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2518,10 +2527,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2535,7 +2544,7 @@
         <v>266</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2549,7 +2558,7 @@
         <v>266</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2563,7 +2572,7 @@
         <v>266</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2577,7 +2586,7 @@
         <v>265</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2591,7 +2600,7 @@
         <v>265</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2605,7 +2614,7 @@
         <v>265</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2619,7 +2628,7 @@
         <v>265</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2633,7 +2642,7 @@
         <v>265</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2647,7 +2656,7 @@
         <v>265</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2661,7 +2670,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2675,7 +2684,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2689,7 +2698,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2703,7 +2712,7 @@
         <v>264</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2717,7 +2726,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2731,7 +2740,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2745,7 +2754,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2756,10 +2765,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2773,7 +2782,7 @@
         <v>265</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2787,7 +2796,7 @@
         <v>265</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2798,10 +2807,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2815,7 +2824,7 @@
         <v>265</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2829,7 +2838,7 @@
         <v>266</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2843,7 +2852,7 @@
         <v>266</v>
       </c>
       <c r="D69" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2857,7 +2866,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2871,7 +2880,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2885,7 +2894,7 @@
         <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2899,7 +2908,7 @@
         <v>265</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2910,10 +2919,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2927,7 +2936,7 @@
         <v>266</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2938,10 +2947,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2955,7 +2964,7 @@
         <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2969,7 +2978,7 @@
         <v>264</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2983,7 +2992,7 @@
         <v>264</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2997,7 +3006,7 @@
         <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3011,7 +3020,7 @@
         <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3022,10 +3031,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3039,7 +3048,7 @@
         <v>266</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3050,10 +3059,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3064,10 +3073,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3081,7 +3090,7 @@
         <v>265</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3092,10 +3101,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3109,7 +3118,7 @@
         <v>266</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3123,7 +3132,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3137,7 +3146,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3151,7 +3160,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3165,7 +3174,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3179,7 +3188,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3193,7 +3202,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3207,7 +3216,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3221,7 +3230,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3235,7 +3244,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3249,7 +3258,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3263,7 +3272,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3277,7 +3286,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3291,7 +3300,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3305,7 +3314,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3319,7 +3328,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3333,7 +3342,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3347,7 +3356,7 @@
         <v>265</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3361,7 +3370,7 @@
         <v>265</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3375,7 +3384,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3389,7 +3398,7 @@
         <v>265</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3403,7 +3412,7 @@
         <v>266</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3417,7 +3426,7 @@
         <v>266</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3428,10 +3437,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3445,7 +3454,7 @@
         <v>264</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3459,7 +3468,7 @@
         <v>266</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3473,7 +3482,7 @@
         <v>266</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3487,7 +3496,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3501,7 +3510,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3515,7 +3524,7 @@
         <v>265</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3529,7 +3538,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3543,7 +3552,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3557,7 +3566,7 @@
         <v>266</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3571,7 +3580,7 @@
         <v>266</v>
       </c>
       <c r="D121" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3585,7 +3594,7 @@
         <v>266</v>
       </c>
       <c r="D122" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3599,7 +3608,7 @@
         <v>266</v>
       </c>
       <c r="D123" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3613,7 +3622,7 @@
         <v>266</v>
       </c>
       <c r="D124" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3627,7 +3636,7 @@
         <v>266</v>
       </c>
       <c r="D125" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3641,7 +3650,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3655,7 +3664,7 @@
         <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3669,7 +3678,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3683,7 +3692,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3697,7 +3706,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3711,7 +3720,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3725,7 +3734,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3739,7 +3748,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3753,7 +3762,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3767,7 +3776,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3778,10 +3787,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3795,7 +3804,7 @@
         <v>265</v>
       </c>
       <c r="D137" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3809,7 +3818,7 @@
         <v>265</v>
       </c>
       <c r="D138" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3823,7 +3832,7 @@
         <v>265</v>
       </c>
       <c r="D139" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3837,7 +3846,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3851,7 +3860,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3862,10 +3871,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D142" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3879,7 +3888,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3893,7 +3902,7 @@
         <v>264</v>
       </c>
       <c r="D144" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3904,10 +3913,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D145" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3918,10 +3927,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D146" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3935,7 +3944,7 @@
         <v>264</v>
       </c>
       <c r="D147" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3946,10 +3955,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3963,7 +3972,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3977,7 +3986,7 @@
         <v>264</v>
       </c>
       <c r="D150" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3991,7 +4000,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4005,7 +4014,7 @@
         <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4019,7 +4028,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4030,10 +4039,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D154" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4047,7 +4056,7 @@
         <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4061,7 +4070,7 @@
         <v>265</v>
       </c>
       <c r="D156" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4075,7 +4084,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4089,7 +4098,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4103,7 +4112,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4117,7 +4126,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4131,7 +4140,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4145,7 +4154,7 @@
         <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4159,7 +4168,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4173,7 +4182,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4187,7 +4196,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4201,7 +4210,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4215,7 +4224,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4229,7 +4238,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4243,7 +4252,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4257,7 +4266,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4271,7 +4280,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4285,7 +4294,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4299,7 +4308,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4313,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4327,7 +4336,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4341,7 +4350,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4355,7 +4364,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4369,7 +4378,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4383,7 +4392,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4397,7 +4406,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4411,7 +4420,7 @@
         <v>264</v>
       </c>
       <c r="D181" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4425,7 +4434,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4439,7 +4448,7 @@
         <v>265</v>
       </c>
       <c r="D183" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4453,7 +4462,7 @@
         <v>265</v>
       </c>
       <c r="D184" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4467,7 +4476,7 @@
         <v>265</v>
       </c>
       <c r="D185" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4481,7 +4490,7 @@
         <v>265</v>
       </c>
       <c r="D186" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4495,7 +4504,7 @@
         <v>265</v>
       </c>
       <c r="D187" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4509,7 +4518,7 @@
         <v>265</v>
       </c>
       <c r="D188" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4523,7 +4532,7 @@
         <v>265</v>
       </c>
       <c r="D189" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4537,7 +4546,7 @@
         <v>265</v>
       </c>
       <c r="D190" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4551,7 +4560,7 @@
         <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4565,7 +4574,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4579,7 +4588,7 @@
         <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4590,10 +4599,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D194" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4607,7 +4616,7 @@
         <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4621,7 +4630,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4635,7 +4644,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4649,7 +4658,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4663,7 +4672,7 @@
         <v>264</v>
       </c>
       <c r="D199" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4677,7 +4686,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4691,7 +4700,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4705,7 +4714,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4719,7 +4728,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4733,7 +4742,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4747,7 +4756,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4758,10 +4767,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D206" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4775,7 +4784,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4789,7 +4798,7 @@
         <v>265</v>
       </c>
       <c r="D208" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4803,7 +4812,7 @@
         <v>265</v>
       </c>
       <c r="D209" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4817,7 +4826,7 @@
         <v>265</v>
       </c>
       <c r="D210" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4831,7 +4840,7 @@
         <v>265</v>
       </c>
       <c r="D211" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4845,7 +4854,7 @@
         <v>265</v>
       </c>
       <c r="D212" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4859,7 +4868,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4873,7 +4882,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4887,7 +4896,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4901,7 +4910,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4915,7 +4924,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4929,7 +4938,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4943,7 +4952,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4957,7 +4966,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4971,7 +4980,7 @@
         <v>264</v>
       </c>
       <c r="D221" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4985,7 +4994,7 @@
         <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4999,7 +5008,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5013,7 +5022,7 @@
         <v>265</v>
       </c>
       <c r="D224" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5027,7 +5036,7 @@
         <v>265</v>
       </c>
       <c r="D225" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5041,7 +5050,7 @@
         <v>265</v>
       </c>
       <c r="D226" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5055,7 +5064,7 @@
         <v>265</v>
       </c>
       <c r="D227" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5069,7 +5078,7 @@
         <v>265</v>
       </c>
       <c r="D228" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5083,7 +5092,7 @@
         <v>265</v>
       </c>
       <c r="D229" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5097,7 +5106,7 @@
         <v>265</v>
       </c>
       <c r="D230" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5108,10 +5117,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5125,7 +5134,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5139,7 +5148,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5153,7 +5162,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5167,7 +5176,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5181,7 +5190,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5195,7 +5204,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5209,7 +5218,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5223,7 +5232,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5237,7 +5246,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5251,7 +5260,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5265,7 +5274,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5279,7 +5288,7 @@
         <v>265</v>
       </c>
       <c r="D243" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5293,7 +5302,7 @@
         <v>265</v>
       </c>
       <c r="D244" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5307,7 +5316,7 @@
         <v>265</v>
       </c>
       <c r="D245" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5321,7 +5330,7 @@
         <v>265</v>
       </c>
       <c r="D246" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5335,7 +5344,7 @@
         <v>265</v>
       </c>
       <c r="D247" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5349,7 +5358,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5360,10 +5369,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D249" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5377,7 +5386,7 @@
         <v>265</v>
       </c>
       <c r="D250" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5391,7 +5400,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5405,7 +5414,7 @@
         <v>264</v>
       </c>
       <c r="D252" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5419,7 +5428,7 @@
         <v>264</v>
       </c>
       <c r="D253" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5430,10 +5439,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D254" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5447,7 +5456,7 @@
         <v>264</v>
       </c>
       <c r="D255" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5461,7 +5470,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
